--- a/lifesync360-platform 설계서 V3.xlsx
+++ b/lifesync360-platform 설계서 V3.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="인증 · 로그인" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="홈 · 점수 · 캠페인" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="추천 · 상품" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="이벤트 · 신청 내역" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="동의 · 설정" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="인프라 · 운영" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="인증 · 로그인" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="홈 · 점수 · 캠페인" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="추천 · 상품" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="이벤트 · 신청 내역" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="동의 · 설정" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="인프라 · 운영" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -572,12 +572,12 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>AWS Systems Manager (Parameter Store)</t>
+          <t>AWS Secrets Manager</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>/lifesync360/jwt-secret (SecureString)</t>
+          <t>ecs-jwt-signing · jwt key</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>AWS Systems Manager (Parameter Store)</t>
+          <t>AWS Secrets Manager</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>/lifesync360/jwt-secret (SecureString)</t>
+          <t>ecs-jwt-signing · jwt key</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>첫 호출 1회만 SSM 조회 후 메모리 캐시. ECS 배포 시 환경변수로 자동 주입</t>
+          <t>첫 호출 1회만 Secrets Manager 조회 후 메모리 캐시. ECS 배포 시 환경변수로 자동 주입</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>입력: 이메일·비밀번호 / 검증: test_login_credentials.csv (5 등급 데모) / 토큰 발급: jwt.encode + SSM /lifesync360/jwt-secret</t>
+          <t>입력: 이메일·비밀번호 / 검증: test_login_credentials.csv (5 등급 데모) / 토큰 발급: jwt.encode + Secrets Manager ecs-jwt-signing</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>추천 정렬에 필요한 본인 점수·등급·NBA 가져오기</t>
+          <t>추천 정렬에 필요한 본인 점수·등급 가져오기</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>등급·종합점수·건강점수·VIP 확률·다음 행동(NBA, 내부 사용)</t>
+          <t>등급·종합점수·건강점수·VIP 확률</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>NBA 매칭되는 룰을 최상단으로 정렬 (내부 가중치)</t>
+          <t>등급·점수·건강조건 기준으로 우선순위 정렬</t>
         </is>
       </c>
     </row>
@@ -2618,17 +2618,17 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>AWS Systems Manager</t>
+          <t>AWS Secrets Manager</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>/lifesync360/jwt-secret</t>
+          <t>ecs-jwt-signing</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>SecureString — ECS task secrets 로 자동 주입</t>
+          <t>JSON 의 jwt key — ECS task secrets 로 자동 주입</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>점수·등급·NBA 등 ML 산출물 저장 테이블</t>
+          <t>점수·등급 등 ML 산출물 저장 테이블</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">

--- a/lifesync360-platform 설계서 V3.xlsx
+++ b/lifesync360-platform 설계서 V3.xlsx
@@ -474,7 +474,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>로그인 · 토큰 발급 (1번 영역 : 시연 진입)</t>
+          <t>로그인 · 토큰 발급 (1번 영역)</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="46" customHeight="1">
+    <row r="4" ht="27" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>계정 검증</t>
@@ -540,22 +540,22 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>입력한 이메일·비밀번호가 5 등급 데모 계정과 일치하는지 확인</t>
+          <t>입력한 이메일·비밀번호를 온프레미스 사용자 DB 에서 조회/검증</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>test_login_credentials.csv (시연용 사전 발급 계정)</t>
+          <t>온프레미스 MySQL (Lambda 경유)</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>login_email + sha256_hex</t>
+          <t>lifesync_onprem.users (Lambda action=login)</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>5 등급 × 1 명 — VIP / GOLD / SILVER / BASIC / CARE (예: user0000924@lifesync.com · DemoVIP01!). 비밀번호는 SHA-256 해시 비교</t>
+          <t>app.py → lifesync-onprem-customer-query Lambda → Private API → ls-db MySQL. 비밀번호는 SHA-256 해시 비교</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>입력: 이메일·비밀번호 / 검증: test_login_credentials.csv (5 등급 데모) / 토큰 발급: jwt.encode + Secrets Manager ecs-jwt-signing</t>
+          <t>입력: 이메일·비밀번호 / 검증: 온프레미스 MySQL (Lambda 경유) / 토큰 발급: jwt.encode + Secrets Manager ecs-jwt-signing</t>
         </is>
       </c>
     </row>

--- a/lifesync360-platform 설계서 V3.xlsx
+++ b/lifesync360-platform 설계서 V3.xlsx
@@ -1328,7 +1328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1400,69 +1400,69 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="27" customHeight="1">
+    <row r="4" ht="46" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>② 캐시 확인</t>
+          <t>② 동의 조회</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>6시간 이내 추천 결과가 있으면 그대로 재사용</t>
+          <t>본인이 동의한 계열사(도메인) 목록 확보 — 미동의 계열사 상품은 추천에서 제외</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>AWS ElastiCache (Redis)</t>
+          <t>Redis 캐시 → Lambda 라이브 → DynamoDB 폴백</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>rec:{global_id}</t>
+          <t>consent:{global_id} / lifesync_onprem.consent</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>캐시 히트 시 SQL 단계 생략 → 응답 빠름</t>
+          <t>캐시(24h TTL) hit → live(Lambda) → DDB row 있으면 전 도메인 폴백 → 셋 다 실패 시 추천 0건(fail-closed)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="27" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>③ 룰 매칭</t>
+          <t>③ 추천 캐시 확인</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>등급·점수·건강조건에 맞는 추천 룰 찾기</t>
+          <t>6시간 이내 추천 결과가 있으면 그대로 재사용</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Aurora MySQL</t>
+          <t>AWS ElastiCache (Redis)</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>recommend_rule</t>
+          <t>rec:{global_id}</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>등급·점수·건강조건 기준으로 우선순위 정렬</t>
+          <t>캐시 히트 시 SQL 단계 생략. cache 결과에도 동의 필터 적용 (stale 방어)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="27" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>④ 교차 추천 보강</t>
+          <t>④ 룰 매칭</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>주 카테고리와 어울리는 다른 카테고리 3개 추가</t>
+          <t>등급·점수·건강조건에 맞는 추천 룰 찾기</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -1472,24 +1472,24 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>cross_sell_rule</t>
+          <t>recommend_rule</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>예: 은행 적금 → 카드·보험 추천 함께</t>
+          <t>등급·점수·건강조건 기준으로 우선순위 정렬</t>
         </is>
       </c>
     </row>
     <row r="7" ht="27" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>⑤ 상품 매칭</t>
+          <t>⑤ 교차 추천 보강</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>카테고리별로 우선순위 상위 2개씩, 최대 10개 추출</t>
+          <t>주 카테고리와 어울리는 다른 카테고리 3개 추가</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -1499,382 +1499,409 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
+          <t>cross_sell_rule</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>예: 은행 적금 → 카드·보험 추천 함께</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="46" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>⑥ 상품 매칭 · 동의 필터</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>카테고리별로 우선순위 상위 2개씩, 최대 10개 추출 + 동의 계열사로 필터링</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Aurora MySQL</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
           <t>product_master + company + category</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>상품·계열사·카테고리 정보 JOIN, 우선순위 기준 정렬</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>⑥ 이력 적재 · 캐시 갱신</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>JOIN 후 WHERE c.company_code IN (동의 도메인 목록) 으로 필터링. 카테고리·우선순위 기준 정렬</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="27" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>⑦ 이력 적재 · 캐시 갱신</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>추천 결과를 이력 테이블에 기록하고 Redis 6시간 캐시</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Aurora MySQL + Redis</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>customer_recommend_history</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>나중에 클릭율·구매율 분석 데이터로 활용</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="1" t="inlineStr">
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>상품 상세 (2번 영역 : 추천 카드 클릭 후)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>기능</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>데이터 소스</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>테이블 / 객체</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>컬럼 / 비고</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="27" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>상품 정보</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>상품 이름·설명·대상등급·위험도·옵션 등 상세 정보</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Aurora MySQL</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>product_master + product_option</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>회사 / 카테고리 정보까지 JOIN 으로 함께 조회</t>
         </is>
       </c>
     </row>
     <row r="13" ht="27" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
+          <t>상품 정보</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>상품 이름·설명·대상등급·위험도·옵션 등 상세 정보</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Aurora MySQL</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>product_master + product_option</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>회사 / 카테고리 정보까지 JOIN 으로 함께 조회</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="27" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
           <t>상품 조회 이벤트</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>상세 페이지 진입 시 자동으로 분석 데이터 적재</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Aurora MySQL</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>customer_dashboard_log</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>/api/event 호출 — 어떤 상품이 많이 보이는지 측정</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="1" t="inlineStr">
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>상품 신청 (3번 영역 : 상품 상세에서 진입)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>기능</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>데이터 소스</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>테이블 / 객체</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>컬럼 / 비고</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="27" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>신청 폼 페이지</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>신청자 정보와 상품 정보를 함께 보여주는 폼 화면</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>프론트엔드 SSR</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>templates/apply.html</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>추가 정보 입력 없이 단순 확인 후 신청 가능</t>
         </is>
       </c>
     </row>
     <row r="18" ht="27" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>신청 처리</t>
+          <t>신청 폼 페이지</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>신청서 접수 + 추천 이력 갱신 + 분석 로그 동시 기록</t>
+          <t>신청자 정보와 상품 정보를 함께 보여주는 폼 화면</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Aurora MySQL</t>
+          <t>프론트엔드 SSR</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>customer_product_application</t>
+          <t>templates/apply.html</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>신청번호 자동 생성 (APP-{시각}-{사용자식별 6자리}), 상태 RECEIVED</t>
+          <t>추가 정보 입력 없이 단순 확인 후 신청 가능</t>
         </is>
       </c>
     </row>
     <row r="19" ht="27" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
+          <t>신청 처리</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>신청서 접수 + 추천 이력 갱신 + 분석 로그 동시 기록</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Aurora MySQL</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>customer_product_application</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>신청번호 자동 생성 (APP-{시각}-{사용자식별 6자리}), 상태 RECEIVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="27" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
           <t>관련 이력 갱신</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>추천에서 들어온 상품인 경우 구매 플래그 자동 업데이트</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>Aurora MySQL</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>customer_recommend_history</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>추천 클릭 → 신청 전환율 분석에 활용</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="1" t="inlineStr">
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="1" t="inlineStr">
         <is>
           <t>API — 추천 · 상품 호출</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>구현 위치</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>엔드포인트</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>데이터 소스</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="27" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
+    <row r="24" ht="46" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>/api/recommendations</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>개인화 추천 top 10 (룰 + 캐시 + 상품 매칭)</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>개인화 추천 top 10 (동의 필터 + 룰 + 캐시 + 상품 매칭)</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>app.py · api_recommendations() — @require_jwt</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>GET /api/recommendations</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>6단계 흐름: DynamoDB 메타 → Redis 캐시 → 룰 매칭 → 교차 추천 → 상품 JOIN → 이력 적재. 캐시 TTL 6시간</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="27" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>/product/&lt;code&gt;</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>상품 상세 페이지 (SSR)</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>app.py · product()</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>GET /product/&lt;product_code&gt;</t>
-        </is>
-      </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Aurora product_master + 회사·카테고리·옵션</t>
+          <t>7단계: DDB 메타 → 동의 조회(cache/live/fallback) → Redis 추천 캐시 → 룰 매칭 → 교차 추천 → 상품 JOIN+동의 도메인 필터 → 이력 적재. 캐시 TTL 6시간</t>
         </is>
       </c>
     </row>
     <row r="25" ht="27" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>/product/&lt;code&gt;/apply</t>
+          <t>/product/&lt;code&gt;</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>상품 신청 폼 페이지 (SSR)</t>
+          <t>상품 상세 페이지 (SSR)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>app.py · product_apply()</t>
+          <t>app.py · product()</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>GET /product/&lt;product_code&gt;/apply</t>
+          <t>GET /product/&lt;product_code&gt;</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Aurora product_master 에서 신청용 상품 정보 추출</t>
+          <t>Aurora product_master + 회사·카테고리·옵션. 옵션은 product_option_template 기반 한글 라벨로 변환 표시</t>
         </is>
       </c>
     </row>
     <row r="26" ht="27" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
+          <t>/product/&lt;code&gt;/apply</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>상품 신청 폼 페이지 (SSR)</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>app.py · product_apply()</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>GET /product/&lt;product_code&gt;/apply</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Aurora product_master 에서 신청용 상품 정보 추출</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="27" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
           <t>/api/product/&lt;code&gt;/apply</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>상품 신청 처리 (Aurora 3개 테이블 동시 갱신)</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>app.py · api_product_apply() — @require_jwt</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>POST /api/product/&lt;product_code&gt;/apply</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>신청서 INSERT + 추천 이력 구매 플래그 UPDATE + 분석 로그 INSERT</t>
         </is>
@@ -1882,10 +1909,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A16:E16"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A22:E22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
